--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SBC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SBC.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Terry (43 L)</t>
+          <t>M. Terry (56 L)</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Tavares (16.0 3PA)</t>
+          <t>M. Tavares (25.0 3PA)</t>
         </is>
       </c>
     </row>
@@ -506,7 +506,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T. Espada (1.615)</t>
+          <t>T. Espada (1.211)</t>
         </is>
       </c>
     </row>
@@ -518,7 +518,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paint Non-RA (35 L)</t>
+          <t>Paint Non-RA (64 L)</t>
         </is>
       </c>
     </row>
@@ -530,7 +530,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paint Non-RA (68.6%)</t>
+          <t>Restricted Area (61.5%)</t>
         </is>
       </c>
     </row>
@@ -571,10 +571,10 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -589,10 +589,10 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -944,53 +944,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.13953488372093</v>
+        <v>1.125</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -1001,115 +1001,115 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>20</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>17</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AE2" t="n">
+      <c r="AN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
         <v>17</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AH2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -1117,11 +1117,11 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
         <v>2</v>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>2</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.304347826086957</v>
+        <v>1.128205128205128</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -1249,11 +1249,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1262,11 +1262,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -1288,11 +1288,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1301,11 +1301,11 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -1317,11 +1317,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1330,11 +1330,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1370,14 +1370,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr">
@@ -1422,53 +1422,53 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O4" t="n">
         <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.285714285714286</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -1479,105 +1479,115 @@
         </is>
       </c>
       <c r="V4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>7</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>57.1%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AH4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AN4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="AH4" t="n">
+      <c r="AT4" t="n">
         <v>7</v>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -1589,7 +1599,7 @@
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>1</v>
@@ -1604,27 +1614,27 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BC4" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1664,53 +1674,53 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
         <v>4</v>
       </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
         <v>5</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1.615384615384615</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -1721,55 +1731,65 @@
         </is>
       </c>
       <c r="V5" t="n">
+        <v>7</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
         <v>6</v>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="AB5" t="n">
         <v>3</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>6</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
@@ -1779,37 +1799,37 @@
         </is>
       </c>
       <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
         <v>6</v>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AT5" t="n">
         <v>3</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV5" t="n">
@@ -1817,7 +1837,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
@@ -1836,7 +1856,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
@@ -1852,7 +1872,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -1901,10 +1921,10 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -1919,10 +1939,10 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -2274,53 +2294,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="n">
         <v>4</v>
       </c>
-      <c r="L2" t="n">
-        <v>3</v>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>5</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.615384615384615</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -2331,55 +2351,65 @@
         </is>
       </c>
       <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
         <v>6</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>3</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>6</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
@@ -2389,37 +2419,37 @@
         </is>
       </c>
       <c r="AN2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
         <v>6</v>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AT2" t="n">
         <v>3</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -2427,7 +2457,7 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX2" t="n">
@@ -2446,7 +2476,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC2" t="n">
@@ -2462,7 +2492,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
@@ -2506,28 +2536,28 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -2548,7 +2578,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.304347826086957</v>
+        <v>1.128205128205128</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -2559,11 +2589,11 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -2572,11 +2602,11 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2585,7 +2615,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -2598,11 +2628,11 @@
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -2611,11 +2641,11 @@
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -2627,11 +2657,11 @@
         </is>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -2640,11 +2670,11 @@
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -2653,7 +2683,7 @@
         </is>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -2672,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -2680,14 +2710,14 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr">
@@ -2718,219 +2748,229 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>291474</t>
+          <t>262518</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I4" t="n">
+        <v>63</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L4" t="n">
         <v>27</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>65.9%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>73.2%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>16</v>
-      </c>
-      <c r="O4" t="n">
-        <v>7</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>23.8%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>76.2%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>9</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="Y4" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AN4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AV4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
         <v>5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -2938,7 +2978,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -2960,220 +3000,220 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>291474</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H5" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="O5" t="n">
+        <v>7</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>69.4%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>16</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AT5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
         <v>3</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>69.8%</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>1.13953488372093</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>17</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AV5" t="n">
-        <v>1</v>
-      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -3182,7 +3222,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG5" t="n">
@@ -3190,7 +3230,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -3231,10 +3271,10 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -3249,10 +3289,10 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="17" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -3604,53 +3644,53 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="O2" t="n">
         <v>7</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1.285714285714286</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
@@ -3661,105 +3701,115 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="AB2" t="n">
         <v>7</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>57.1%</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AK2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AN2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>Corner 3 Right</t>
         </is>
       </c>
-      <c r="AH2" t="n">
+      <c r="AT2" t="n">
         <v>7</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="AV2" t="n">
@@ -3771,7 +3821,7 @@
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY2" t="n">
         <v>1</v>
@@ -3786,27 +3836,27 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
+          <t>800.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
           <t>600.0%</t>
         </is>
       </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -3846,53 +3896,53 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>1.13953488372093</v>
+        <v>1.125</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
@@ -3903,115 +3953,115 @@
         </is>
       </c>
       <c r="V3" t="n">
+        <v>20</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
         <v>17</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="Y3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AH3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="AE3" t="n">
+      <c r="AN3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
         <v>17</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="AH3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="AT3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="AV3" t="n">
@@ -4019,11 +4069,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY3" t="n">
         <v>2</v>
@@ -4038,27 +4088,27 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD3" t="n">
         <v>2</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>700.0%</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -4098,53 +4148,53 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="L4" t="n">
-        <v>3</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O4" t="n">
         <v>5</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>1.615384615384615</v>
+        <v>1.210526315789474</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -4155,55 +4205,65 @@
         </is>
       </c>
       <c r="V4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
         <v>6</v>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="AB4" t="n">
         <v>3</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>66.7%</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>6</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="inlineStr"/>
@@ -4213,37 +4273,37 @@
         </is>
       </c>
       <c r="AN4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>Corner 3 Left</t>
         </is>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AT4" t="n">
         <v>3</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
       <c r="AV4" t="n">
@@ -4251,7 +4311,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="AX4" t="n">
@@ -4270,7 +4330,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>600.0%</t>
         </is>
       </c>
       <c r="BC4" t="n">
@@ -4286,7 +4346,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG4" t="n">
@@ -4330,28 +4390,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="I5" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -4372,7 +4432,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>1.304347826086957</v>
+        <v>1.128205128205128</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
@@ -4383,11 +4443,11 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -4396,11 +4456,11 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -4409,7 +4469,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -4422,11 +4482,11 @@
         </is>
       </c>
       <c r="AE5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -4435,11 +4495,11 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -4451,11 +4511,11 @@
         </is>
       </c>
       <c r="AN5" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -4464,11 +4524,11 @@
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -4477,7 +4537,7 @@
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -4496,7 +4556,7 @@
         <v>2</v>
       </c>
       <c r="AY5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -4504,14 +4564,14 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BC5" t="n">
         <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr">
@@ -4535,7 +4595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4561,10 +4621,10 @@
     <col width="19" customWidth="1" min="21" max="21"/>
     <col width="16" customWidth="1" min="22" max="22"/>
     <col width="16" customWidth="1" min="23" max="23"/>
-    <col width="19" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
-    <col width="14" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="16" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="22" customWidth="1" min="30" max="30"/>
@@ -4579,10 +4639,10 @@
     <col width="19" customWidth="1" min="39" max="39"/>
     <col width="20" customWidth="1" min="40" max="40"/>
     <col width="20" customWidth="1" min="41" max="41"/>
-    <col width="19" customWidth="1" min="42" max="42"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
     <col width="20" customWidth="1" min="43" max="43"/>
     <col width="20" customWidth="1" min="44" max="44"/>
-    <col width="16" customWidth="1" min="45" max="45"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
     <col width="20" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
@@ -4920,134 +4980,134 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_T._ESPADA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>291474</t>
+          <t>244169</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>T. Espada</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>23</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>9</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>10</v>
       </c>
-      <c r="I2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1.210526315789474</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>7</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="AB2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>16</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE2" t="n">
         <v>7</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>23.8%</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>76.2%</t>
-        </is>
-      </c>
-      <c r="S2" t="n">
-        <v>1.285714285714286</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>9</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="Y2" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="AB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AH2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AE2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>57.1%</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr"/>
@@ -5059,88 +5119,88 @@
         </is>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="AT2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="AV2" t="n">
         <v>4</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AV2" t="n">
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3</v>
       </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
         <v>3</v>
       </c>
-      <c r="AY2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>200.0%</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BD2" t="n">
         <v>3</v>
       </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>600.0%</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1</v>
-      </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5162,220 +5222,220 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>291474</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>30.6%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>69.4%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>16</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AB3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AE3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="AT3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="AV3" t="n">
         <v>3</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>69.8%</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>30.2%</t>
-        </is>
-      </c>
-      <c r="S3" t="n">
-        <v>1.13953488372093</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>17</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="Y3" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AB3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AE3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>58.8%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="AT3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="AV3" t="n">
-        <v>1</v>
-      </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="AX3" t="n">
         <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>800.0%</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -5384,13 +5444,265 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="BG3" t="n">
         <v>4</v>
       </c>
       <c r="BH3" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SBC_M._TERRY</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>262518</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>M. Terry</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>56</v>
+      </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" t="n">
+        <v>63</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>53.6%</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>41</v>
+      </c>
+      <c r="L4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>65.9%</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>73.2%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>26.8%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>20</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AB4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>700.0%</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="inlineStr">
         <is>
           <t>300.0%</t>
         </is>
@@ -5562,27 +5874,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.371428571428571</v>
+        <v>1.21875</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -5592,7 +5904,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -5603,7 +5915,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -5611,7 +5923,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -5619,7 +5931,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -5641,41 +5953,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.151515151515152</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J3" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -5686,7 +5998,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -5694,7 +6006,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>500.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -5702,7 +6014,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -5724,68 +6036,68 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="J4" t="n">
+        <v>39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>24</v>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>11</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>500.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -5807,45 +6119,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.666666666666667</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>9</v>
-      </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>4</v>
@@ -5860,11 +6172,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>400.0%</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5884,41 +6202,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5714285714285714</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -5929,7 +6247,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -5937,7 +6255,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>600.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -5965,7 +6283,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
         <v>2</v>
@@ -5975,11 +6293,11 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -5988,14 +6306,14 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
         <v>2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -6006,7 +6324,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -6014,7 +6332,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -6031,7 +6349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6182,11 +6500,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
         <v>24</v>
@@ -6196,14 +6514,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.371428571428571</v>
+        <v>1.230769230769231</v>
       </c>
       <c r="J2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K2" t="n">
         <v>24</v>
@@ -6216,14 +6534,14 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -6231,7 +6549,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -6239,7 +6557,7 @@
         </is>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -6265,31 +6583,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.151515151515152</v>
+        <v>1.21875</v>
       </c>
       <c r="J3" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -6299,14 +6617,14 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -6314,15 +6632,15 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -6352,21 +6670,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.8235294117647058</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6375,14 +6693,14 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="M4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -6410,6 +6728,89 @@
       <c r="U4" t="inlineStr">
         <is>
           <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7.7%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>600.0%</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>400.0%</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6593,46 +6994,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>322841</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H2" t="n">
+        <v>27</v>
+      </c>
+      <c r="I2" t="n">
         <v>17</v>
       </c>
-      <c r="I2" t="n">
-        <v>10</v>
-      </c>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.176470588235294</v>
+        <v>1.259259259259259</v>
       </c>
       <c r="M2" t="n">
+        <v>27</v>
+      </c>
+      <c r="N2" t="n">
         <v>17</v>
-      </c>
-      <c r="N2" t="n">
-        <v>10</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -6642,7 +7043,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -6653,7 +7054,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -6661,7 +7062,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -6669,7 +7070,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6691,46 +7092,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SBC_D._HALL</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>262518</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.571428571428571</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -6740,7 +7141,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -6751,7 +7152,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -6759,7 +7160,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -6767,7 +7168,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -6804,41 +7205,41 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="M4" t="n">
+        <v>17</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
-        <v>12</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3</v>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -6849,7 +7250,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -6857,7 +7258,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -6865,7 +7266,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -6887,83 +7288,83 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>291474</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>16</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>72.7%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.454545454545455</v>
-      </c>
-      <c r="M5" t="n">
-        <v>11</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="R5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>400.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -6985,17 +7386,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>291474</t>
+          <t>262518</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -7004,7 +7405,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -7014,11 +7415,11 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7027,29 +7428,29 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="R6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -7057,11 +7458,11 @@
         </is>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
     </row>
@@ -7102,27 +7503,27 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M7" t="n">
         <v>8</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1.142857142857143</v>
-      </c>
-      <c r="M7" t="n">
-        <v>7</v>
-      </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -7132,7 +7533,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -7196,41 +7597,41 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.714285714285714</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
+        <v>8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4</v>
+      </c>
+      <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="R8" t="n">
@@ -7241,7 +7642,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U8" t="n">
@@ -7249,7 +7650,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W8" t="n">
@@ -7257,7 +7658,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
     </row>
@@ -7279,40 +7680,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SBC_T._ESPADA</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>244169</t>
+          <t>291474</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>T. Espada</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7321,39 +7722,329 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SBC_T._ESPADA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>244169</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>T. Espada</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>36.8%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SBC_T._ESPADA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>244169</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>T. Espada</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>6</v>
       </c>
-      <c r="P9" t="n">
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>46.2%</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>400.0%</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SBC_H._SMITH</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>H. Smith</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>5</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -7370,7 +8061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -7539,17 +8230,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SBC_D._HALL</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>322841</t>
+          <t>262518</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Hall</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7558,27 +8249,27 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.571428571428571</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -7588,14 +8279,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="R2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -7603,7 +8294,7 @@
         </is>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -7611,7 +8302,7 @@
         </is>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -7637,17 +8328,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>322841</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7656,27 +8347,27 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.454545454545455</v>
+        <v>1.259259259259259</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -7686,14 +8377,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="R3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -7701,15 +8392,15 @@
         </is>
       </c>
       <c r="U3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>200.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -7735,17 +8426,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_D._HALL</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>322841</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>D. Hall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7754,27 +8445,27 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="n">
         <v>10</v>
       </c>
-      <c r="J4" t="n">
-        <v>20</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.176470588235294</v>
+        <v>1.25</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -7784,14 +8475,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="R4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -7799,15 +8490,15 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -7833,56 +8524,56 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SBC_M._TAVARES</t>
+          <t>SBC_M._TERRY</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>291474</t>
+          <t>262518</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M. Tavares</t>
+          <t>M. Terry</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" t="n">
+        <v>12</v>
+      </c>
+      <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -7901,7 +8592,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -7931,56 +8622,56 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SBC_M._TERRY</t>
+          <t>SBC_M._TAVARES</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>262518</t>
+          <t>291474</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>M. Terry</t>
+          <t>M. Tavares</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
+        <v>8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
-        <v>12</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -7991,7 +8682,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>300.0%</t>
+          <t>200.0%</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -7999,13 +8690,209 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>400.0%</t>
+          <t>300.0%</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="inlineStr">
+        <is>
+          <t>200.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SBC_M._TERRY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>262518</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M. Terry</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>14</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sampaense Inspecentro</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SBC_M._TAVARES</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>291474</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M. Tavares</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>300.0%</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>400.0%</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>300.0%</t>
         </is>
